--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:38:17+00:00</t>
+    <t>2026-09-30T10:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:37:32+00:00</t>
+    <t>2026-09-30T12:38:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:38:48+00:00</t>
+    <t>2026-09-30T12:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:48:42+00:00</t>
+    <t>2026-09-30T13:49:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T13:49:36+00:00</t>
+    <t>2026-09-30T15:53:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T15:53:21+00:00</t>
+    <t>2026-10-01T13:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:59:48+00:00</t>
+    <t>2026-10-01T15:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T15:54:53+00:00</t>
+    <t>2026-10-05T14:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T14:15:07+00:00</t>
+    <t>2026-10-05T14:43:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T14:43:16+00:00</t>
+    <t>2026-10-05T15:33:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T15:33:11+00:00</t>
+    <t>2026-10-07T16:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T16:07:50+00:00</t>
+    <t>2026-10-08T08:40:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
